--- a/ig/DM-JUIN-2026/ValueSet-jdv-j390-origine-interruption-exercice-rpps.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-jdv-j390-origine-interruption-exercice-rpps.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L’origine d’une interruption d’exercice correspond à l’autorité juridique ou administrative ayant prononcé la mesure. Cette information permet d’identifier le cadre dans lequel la décision a été prise et d’en comprendre le contexte. Elle facilite son interprétation, notamment pour apprécier les modalités d’application de la mesure (portée, exécution, éventuels recours).</t>
+    <t>Jeu de valeurs à destination du RPPS : L’origine d’une interruption d’exercice correspond à l’autorité juridique ou administrative ayant prononcé la mesure. Cette information permet d’identifier le cadre dans lequel la décision a été prise et d’en comprendre le contexte. Elle facilite son interprétation, notamment pour apprécier les modalités d’application de la mesure (portée, exécution, éventuels recours).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,16 +102,34 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Conseil de l'Ordre</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Agence Régional de Santé</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Agence régionale de santé</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Chambre disciplinaire de l’ordre</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Conseil de l’ordre</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Section des assurances sociales de l’ordre</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Tribunal</t>
   </si>
   <si>
     <t/>
@@ -120,7 +138,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r436-origine-interruption-exercice</t>
   </si>
 </sst>
 </file>
@@ -384,7 +402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -420,15 +438,39 @@
         <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
